--- a/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_levels_cosine_nearest_top_vs_zero.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_levels_cosine_nearest_top_vs_zero.xlsx
@@ -507,13 +507,13 @@
         <v>7.126087697599305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02685638041386324</v>
+        <v>-0.04931583105508341</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0269142526550989</v>
+        <v>0.04937370329631906</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>7.131018938021787</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.02689033518016854</v>
+        <v>-0.04934978582138871</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0268802978887936</v>
+        <v>0.04933974853001376</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>7.119546091650808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.02685861030921517</v>
+        <v>-0.04931806095043533</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02691202275974698</v>
+        <v>0.04937147340096714</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>7.100810110970246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.02687281341755616</v>
+        <v>-0.04933226405877632</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02689781965140598</v>
+        <v>0.04935727029262615</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>7.067168878436031</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.02686760823681817</v>
+        <v>-0.04932705887803834</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02690302483214397</v>
+        <v>0.04936247547336414</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>7.032863274890606</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02686519110919301</v>
+        <v>-0.04932464175041317</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02690544195976914</v>
+        <v>0.0493648926009893</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>6.993709338701228</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.02687348686073294</v>
+        <v>-0.0493329375019531</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0268971462082292</v>
+        <v>0.04935659684944937</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>6.983724528837069</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.02686375886858601</v>
+        <v>-0.04932320950980617</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02690687420037614</v>
+        <v>0.0493663248415963</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>6.960628141174349</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02686301265827558</v>
+        <v>-0.04932246329949574</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02690762041068657</v>
+        <v>0.04936707105190673</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>6.94783602095504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.02688398038639734</v>
+        <v>-0.04934343102761751</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0268866526825648</v>
+        <v>0.04934610332378497</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>6.922126041201317</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.02685629584531375</v>
+        <v>-0.04931574648653391</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0269143372236484</v>
+        <v>0.04937378786486856</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>6.89075156037469</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0268739180276369</v>
+        <v>-0.04933336866885706</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02689671504132525</v>
+        <v>0.04935616568254541</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>6.900103308668752</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.02686300307304874</v>
+        <v>-0.0493224537142689</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02690762999591341</v>
+        <v>0.04936708063713357</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>6.885252288781944</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.02687138234242488</v>
+        <v>-0.04933083298364504</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02689925072653727</v>
+        <v>0.04935870136775743</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>6.87573475618544</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.02686060426618093</v>
+        <v>-0.04932005490740109</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02691002880278122</v>
+        <v>0.04936947944400138</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>6.844228900034523</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.02687555296948281</v>
+        <v>-0.04933500361070297</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02689508009947934</v>
+        <v>0.0493545307406995</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>6.815347014069063</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.026865316479127</v>
+        <v>-0.04932476712034716</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02690531658983515</v>
+        <v>0.04936476723105531</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>6.796059343037657</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.02687385606277166</v>
+        <v>-0.04933330670399182</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02689677700619049</v>
+        <v>0.04935622764741065</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>6.817135745764311</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.026846886606062</v>
+        <v>-0.04930633724728217</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02692374646290014</v>
+        <v>0.04938319710412031</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>6.83849912124536</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.02688531653448107</v>
+        <v>-0.04934476717570124</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02688531653448107</v>
+        <v>0.04934476717570124</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>6.825366919713312</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.01782370673877205</v>
+        <v>-0.04028315737999221</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0359469263301901</v>
+        <v>0.05840637697141026</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>6.815897339622838</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.006788370648866237</v>
+        <v>-0.0292478212900864</v>
       </c>
       <c r="K23" t="n">
-        <v>0.04698226242009591</v>
+        <v>0.06944171306131608</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>6.806014470275789</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.003705743073068656</v>
+        <v>-0.02616519371428882</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05006488999589349</v>
+        <v>0.07252434063711366</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>6.78909662269687</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004123955275085845</v>
+        <v>-0.01833549536613432</v>
       </c>
       <c r="K25" t="n">
-        <v>0.057894588344048</v>
+        <v>0.08035403898526816</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>6.825757032673978</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.009159743367385519</v>
+        <v>-0.03161919400860568</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04461088970157663</v>
+        <v>0.0670703403427968</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>6.818453318357642</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0005425646344517261</v>
+        <v>-0.02191688600676844</v>
       </c>
       <c r="K27" t="n">
-        <v>0.05431319770341388</v>
+        <v>0.07677264834463404</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>6.789309752638157</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02016294001537338</v>
+        <v>-0.002296510625846786</v>
       </c>
       <c r="K28" t="n">
-        <v>0.07393357308433553</v>
+        <v>0.09639302372555569</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>6.757856160230959</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02878755452673181</v>
+        <v>0.006328103885511645</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08255818759569396</v>
+        <v>0.1050176382369141</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>6.750049924385731</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J30" t="n">
-        <v>0.02398563727101726</v>
+        <v>0.001526186629797095</v>
       </c>
       <c r="K30" t="n">
-        <v>0.07775627033997941</v>
+        <v>0.1002157209811996</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>6.744828592376146</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02689099789856746</v>
+        <v>0.004431547257347297</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08066163096752961</v>
+        <v>0.1031210816087498</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>6.756580126087248</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J32" t="n">
-        <v>0.03108856626248651</v>
+        <v>0.008629115621266344</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08485919933144866</v>
+        <v>0.1073186499726688</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>6.768440331274862</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03709529796876447</v>
+        <v>0.01463584732754431</v>
       </c>
       <c r="K33" t="n">
-        <v>0.09086593103772662</v>
+        <v>0.1133253816789468</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>6.764660560599898</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0453089169399548</v>
+        <v>0.02284946629873464</v>
       </c>
       <c r="K34" t="n">
-        <v>0.09907955000891695</v>
+        <v>0.1215390006501371</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>6.77587543287222</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J35" t="n">
-        <v>0.04367220038953538</v>
+        <v>0.02121274974831523</v>
       </c>
       <c r="K35" t="n">
-        <v>0.09744283345849754</v>
+        <v>0.1199022840997177</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>6.763753229052751</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04870810778938699</v>
+        <v>0.02624865714816683</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1024787408583491</v>
+        <v>0.1249381914995693</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>6.753318646496826</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J37" t="n">
-        <v>0.04906946849128006</v>
+        <v>0.0266100178500599</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1028401015602422</v>
+        <v>0.1252995522014624</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>6.773870540945235</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J38" t="n">
-        <v>0.04117940585247064</v>
+        <v>0.01871995521125048</v>
       </c>
       <c r="K38" t="n">
-        <v>0.09495003892143279</v>
+        <v>0.117409489562653</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>6.764890726551868</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J39" t="n">
-        <v>0.04529876655075808</v>
+        <v>0.02283931590953792</v>
       </c>
       <c r="K39" t="n">
-        <v>0.09906939961972024</v>
+        <v>0.1215288502609404</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>6.760049415700732</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04683390583053475</v>
+        <v>0.02437445518931459</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1006045388994969</v>
+        <v>0.1230639895407171</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>6.729892817568365</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J41" t="n">
-        <v>0.05648624366094372</v>
+        <v>0.03402679301972356</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1102568767299059</v>
+        <v>0.132716327371126</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>6.709372479113942</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J42" t="n">
-        <v>0.05507631399463646</v>
+        <v>0.0326168633534163</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1088469470635986</v>
+        <v>0.1313063977048188</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>6.691514997318452</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J43" t="n">
-        <v>0.05580236398012266</v>
+        <v>0.0333429133389025</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1095729970490848</v>
+        <v>0.132032447690305</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>6.70881831354767</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J44" t="n">
-        <v>0.05541550877033989</v>
+        <v>0.03295605812911973</v>
       </c>
       <c r="K44" t="n">
-        <v>0.109186141839302</v>
+        <v>0.1316455924805222</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>6.73332992482224</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J45" t="n">
-        <v>0.05517834203890297</v>
+        <v>0.03271889139768281</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1089489751078651</v>
+        <v>0.1314084257490853</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>6.726465349444537</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J46" t="n">
-        <v>0.05787386354689543</v>
+        <v>0.03541441290567527</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1116444966158576</v>
+        <v>0.1341039472570777</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>6.733490353554068</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J47" t="n">
-        <v>0.06017628444573501</v>
+        <v>0.03771683380451486</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1139469175146972</v>
+        <v>0.1364063681559173</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>6.721287493017218</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07216892145381885</v>
+        <v>0.0497094708125987</v>
       </c>
       <c r="K48" t="n">
-        <v>0.125939554522781</v>
+        <v>0.1483990051640012</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>6.720820791276677</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06656431028565839</v>
+        <v>0.04410485964443823</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1203349433546205</v>
+        <v>0.1427943939958407</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>6.736368427801649</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J50" t="n">
-        <v>0.06395109039188478</v>
+        <v>0.04149163975066462</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1177217234608469</v>
+        <v>0.1401811741020671</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>6.723919842003034</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J51" t="n">
-        <v>0.08175065644080641</v>
+        <v>0.05929120579958625</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1355212895097685</v>
+        <v>0.1579807401509887</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>6.715321061458185</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J52" t="n">
-        <v>0.08416598305285321</v>
+        <v>0.06170653241163305</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1379366161218153</v>
+        <v>0.1603960667630355</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>6.679552656350155</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J53" t="n">
-        <v>0.09176373179658297</v>
+        <v>0.0693042811553628</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1455343648655451</v>
+        <v>0.1679938155067653</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>6.662972191103021</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J54" t="n">
-        <v>0.09398614805019738</v>
+        <v>0.07152669740897721</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1477567811191595</v>
+        <v>0.1702162317603797</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>6.645697589772843</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J55" t="n">
-        <v>0.09738444749763202</v>
+        <v>0.07492499685641185</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1511550805665942</v>
+        <v>0.1736145312078143</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>6.669171371326142</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J56" t="n">
-        <v>0.09745064850605915</v>
+        <v>0.07499119786483899</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1512212815750213</v>
+        <v>0.1736807322162415</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>6.687991230589503</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J57" t="n">
-        <v>0.09903480776691191</v>
+        <v>0.07657535712569175</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1528054408358741</v>
+        <v>0.1752648914770942</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>6.674440913556873</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1122183141960227</v>
+        <v>0.08975886355480256</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1659889472649849</v>
+        <v>0.188448397906205</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>6.680698456100704</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1114972303742515</v>
+        <v>0.08903777973303129</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1652678634432136</v>
+        <v>0.1877273140844338</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>6.67078687616881</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1200720846737709</v>
+        <v>0.09761263403255072</v>
       </c>
       <c r="K60" t="n">
-        <v>0.173842717742733</v>
+        <v>0.1963021683839532</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>6.673889773862733</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1082039616460578</v>
+        <v>0.0857445110048376</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1619745947150199</v>
+        <v>0.1844340453562401</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>6.673389384606637</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1196729447173335</v>
+        <v>0.09721349407611335</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1734435777862957</v>
+        <v>0.1959030284275158</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>6.676303545367765</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1201297165621889</v>
+        <v>0.09767026592096872</v>
       </c>
       <c r="K63" t="n">
-        <v>0.173900349631151</v>
+        <v>0.1963598002723712</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>6.666547269040468</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0137169982318781</v>
+        <v>0.02517590162025573</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1354778330431803</v>
+        <v>0.1130183824019602</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1892484661121425</v>
+        <v>0.2117079167533626</v>
       </c>
     </row>
   </sheetData>
